--- a/recources/project/wheelchair/国市创结题成果.xlsx
+++ b/recources/project/wheelchair/国市创结题成果.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="21550" windowHeight="10080"/>
   </bookViews>
   <sheets>
     <sheet name="2025年第二批国家级（市级）大学生创业训练、创业实践项目结题" sheetId="1" r:id="rId1"/>
@@ -4261,7 +4261,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4441,20 +4441,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="136"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="MS Gothic"/>
       <charset val="128"/>
@@ -4465,13 +4451,26 @@
       <name val="Noto Sans SC"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -4807,7 +4806,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4831,16 +4830,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -4849,89 +4848,89 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4951,6 +4950,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5482,17 +5487,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:J45"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="2" width="14.775" customWidth="1"/>
-    <col min="3" max="3" width="13.2166666666667" customWidth="1"/>
-    <col min="4" max="4" width="53.3333333333333" customWidth="1"/>
-    <col min="5" max="5" width="12.3333333333333" customWidth="1"/>
-    <col min="6" max="6" width="21.5583333333333" customWidth="1"/>
+    <col min="2" max="2" width="14.7727272727273" customWidth="1"/>
+    <col min="3" max="3" width="13.2181818181818" customWidth="1"/>
+    <col min="4" max="4" width="53.3363636363636" customWidth="1"/>
+    <col min="5" max="5" width="12.3363636363636" customWidth="1"/>
+    <col min="6" max="6" width="21.5545454545455" customWidth="1"/>
     <col min="7" max="7" width="20" customWidth="1"/>
-    <col min="8" max="8" width="71.1083333333333" style="1" customWidth="1"/>
-    <col min="9" max="9" width="20.3333333333333" customWidth="1"/>
-    <col min="10" max="10" width="12.3333333333333" customWidth="1"/>
+    <col min="8" max="8" width="71.1090909090909" style="1" customWidth="1"/>
+    <col min="9" max="9" width="20.3363636363636" customWidth="1"/>
+    <col min="10" max="10" width="12.3363636363636" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="63" customHeight="1" spans="1:10">
@@ -6054,34 +6059,34 @@
       </c>
     </row>
     <row r="19" ht="22.95" customHeight="1" spans="1:10">
-      <c r="A19" s="5">
+      <c r="A19" s="7">
         <v>17</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="C19" s="5">
+      <c r="C19" s="7">
         <v>2025</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E19" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="F19" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="G19" s="6">
+      <c r="G19" s="8">
         <v>20234890</v>
       </c>
-      <c r="H19" s="6" t="s">
+      <c r="H19" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="I19" s="6" t="s">
+      <c r="I19" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="J19" s="6" t="s">
+      <c r="J19" s="8" t="s">
         <v>33</v>
       </c>
     </row>
@@ -6432,7 +6437,7 @@
       <c r="D31" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="E31" s="7" t="s">
+      <c r="E31" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F31" s="6" t="s">
